--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487591_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487591_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7085</v>
+        <v>7.6846</v>
       </c>
       <c r="E2" t="n">
-        <v>7.394</v>
+        <v>7.2379</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3146</v>
+        <v>0.4467</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1855</v>
+        <v>7.6156</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2257</v>
+        <v>-0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4112</v>
+        <v>7.7524</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8953</v>
+        <v>8.76</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5407</v>
+        <v>1.2523</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3546</v>
+        <v>7.5077</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7098</v>
+        <v>-1.1444</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7664</v>
+        <v>-1.3891</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0566</v>
+        <v>0.2447</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3582</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3582</v>
+        <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5051</v>
+        <v>-0.7862</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2166</v>
+        <v>-0.0892</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7115</v>
+        <v>-0.697</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6597</v>
+        <v>2.2134</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2821</v>
+        <v>2.4477</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3776</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6443</v>
+        <v>5.8489</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1158</v>
+        <v>5.4526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5284</v>
+        <v>0.3963</v>
       </c>
       <c r="G3" t="n">
-        <v>7.6156</v>
+        <v>3.1855</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1368</v>
+        <v>-0.2257</v>
       </c>
       <c r="I3" t="n">
-        <v>7.7524</v>
+        <v>3.4112</v>
       </c>
       <c r="J3" t="n">
-        <v>8.76</v>
+        <v>3.8953</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2523</v>
+        <v>1.5407</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5077</v>
+        <v>2.3546</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1444</v>
+        <v>-0.7098</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3891</v>
+        <v>-1.7664</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2447</v>
+        <v>1.0566</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3582</v>
+        <v>1.3582</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.8806</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5224</v>
+        <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8266</v>
+        <v>0.6455</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2113</v>
+        <v>1.2752</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6152</v>
+        <v>-0.6297</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2134</v>
+        <v>0.6597</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4477</v>
+        <v>0.2821</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2343</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.663</v>
+        <v>4.6023</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4886</v>
+        <v>1.5096</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1744</v>
+        <v>3.0927</v>
       </c>
       <c r="G4" t="n">
         <v>2.9045</v>
@@ -766,13 +766,13 @@
         <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5153</v>
+        <v>0.4545</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3656</v>
+        <v>0.3866</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1497</v>
+        <v>0.0679</v>
       </c>
       <c r="V4" t="n">
         <v>2.2134</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5022</v>
+        <v>1.3346</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4771</v>
+        <v>1.6429</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0251</v>
+        <v>-0.3083</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6895</v>
+        <v>1.2017</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1747</v>
+        <v>-0.753</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8642</v>
+        <v>1.9548</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0521</v>
+        <v>1.5033</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3213</v>
+        <v>0.0824</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7307</v>
+        <v>1.4209</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3625</v>
+        <v>-0.3015</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.496</v>
+        <v>-0.8354</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1335</v>
+        <v>0.5339</v>
       </c>
       <c r="P5" t="n">
         <v>0.194</v>
@@ -844,13 +844,13 @@
         <v>0.194</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6187</v>
+        <v>-0.0611</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4251</v>
+        <v>0.1396</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1936</v>
+        <v>-0.2007</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.298</v>
+        <v>1.2475</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4427</v>
+        <v>1.2769</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1447</v>
+        <v>-0.0294</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2017</v>
+        <v>0.6895</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.753</v>
+        <v>-0.1747</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9548</v>
+        <v>0.8642</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5033</v>
+        <v>1.0521</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0824</v>
+        <v>0.3213</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4209</v>
+        <v>0.7307</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3015</v>
+        <v>-0.3625</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8354</v>
+        <v>-0.496</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5339</v>
+        <v>0.1335</v>
       </c>
       <c r="P6" t="n">
         <v>0.194</v>
@@ -922,13 +922,13 @@
         <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0978</v>
+        <v>0.3639</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0606</v>
+        <v>0.2249</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0372</v>
+        <v>0.1391</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1932</v>
+        <v>-2.4094</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0122</v>
+        <v>-0.7633</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.181</v>
+        <v>-1.6462</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2639</v>
+        <v>0.7295</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1553</v>
+        <v>-2.3604</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8913</v>
+        <v>3.0899</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3419</v>
+        <v>1.7118</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3048</v>
+        <v>-0.8609</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6467</v>
+        <v>2.5727</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6058</v>
+        <v>-0.9823</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8504</v>
+        <v>-1.4995</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2447</v>
+        <v>0.5172</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1344</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8806</v>
+        <v>-2.9105</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>0.205</v>
+        <v>-0.1971</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2445</v>
+        <v>-0.1287</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0394</v>
+        <v>-0.0684</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1657</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2821</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2523</v>
+        <v>-2.5082</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9803</v>
+        <v>-1.8911</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.272</v>
+        <v>-0.6171</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6029</v>
+        <v>-0.2639</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1969</v>
+        <v>-2.1553</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.406</v>
+        <v>1.8913</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0206</v>
+        <v>1.3419</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0206</v>
+        <v>-0.3048</v>
       </c>
       <c r="L8" t="n">
+        <v>1.6467</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1.6058</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1.8504</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2447</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-2.1344</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-3.8806</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.7463</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.1099</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.4755</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>-0.6235000000000001</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.2175</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.406</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-1.7463</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-1.9403</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.2912</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.0606</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.2306</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.6119</v>
-      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6119</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7525</v>
+        <v>-3.0977</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7247</v>
+        <v>-1.8802</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0277</v>
+        <v>-1.2175</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7295</v>
+        <v>-0.6029</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3604</v>
+        <v>-0.1969</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0899</v>
+        <v>-0.406</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7118</v>
+        <v>0.0206</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8609</v>
+        <v>0.0206</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5727</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9823</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4995</v>
+        <v>-0.2175</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5172</v>
+        <v>-0.406</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7761</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1344</v>
+        <v>0.194</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5401</v>
+        <v>-0.1365</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0902</v>
+        <v>0.0395</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.45</v>
+        <v>-0.1761</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1657</v>
+        <v>-0.6119</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7298</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7872</v>
+        <v>-5.2662</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7197</v>
+        <v>-3.4985</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0675</v>
+        <v>-1.7677</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8499</v>
@@ -1234,13 +1234,13 @@
         <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8791</v>
+        <v>-0.3581</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1839</v>
+        <v>0.4051</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.063</v>
+        <v>-0.7632</v>
       </c>
       <c r="V10" t="n">
         <v>-1.506</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.830800000000002</v>
+        <v>7.436399999999996</v>
       </c>
       <c r="E11" t="n">
-        <v>8.481300000000001</v>
+        <v>9.0868</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.650399999999999</v>
+        <v>-1.650500000000001</v>
       </c>
       <c r="G11" t="n">
         <v>13.6096</v>
@@ -1288,7 +1288,7 @@
         <v>21.4492</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9559000000000004</v>
+        <v>0.9559</v>
       </c>
       <c r="L11" t="n">
         <v>20.4933</v>
@@ -1312,10 +1312,10 @@
         <v>12.612</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7907000000000002</v>
+        <v>-0.185</v>
       </c>
       <c r="T11" t="n">
-        <v>2.013</v>
+        <v>2.6186</v>
       </c>
       <c r="U11" t="n">
         <v>-2.8036</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.0868</v>
+        <v>2.6408</v>
       </c>
       <c r="E12" t="n">
-        <v>4.7118</v>
+        <v>4.2113</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6249</v>
+        <v>-1.5704</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1005</v>
@@ -1390,13 +1390,13 @@
         <v>3.6866</v>
       </c>
       <c r="S12" t="n">
-        <v>0.947</v>
+        <v>0.501</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3492</v>
+        <v>0.8487</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4022</v>
+        <v>-0.3477</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2821</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.962</v>
+        <v>2.636</v>
       </c>
       <c r="E13" t="n">
-        <v>1.656</v>
+        <v>3.0574</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.694</v>
+        <v>-0.4214</v>
       </c>
       <c r="G13" t="n">
         <v>3.1126</v>
@@ -1468,13 +1468,13 @@
         <v>3.6866</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8192</v>
+        <v>-0.1452</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2596</v>
+        <v>0.1418</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5596</v>
+        <v>-0.2871</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8836</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7265</v>
+        <v>1.2275</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6332</v>
+        <v>1.434</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.2065</v>
       </c>
       <c r="G14" t="n">
         <v>-2.0124</v>
@@ -1546,13 +1546,13 @@
         <v>2.5224</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2492</v>
+        <v>0.2518</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7874</v>
+        <v>0.0134</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5382</v>
+        <v>0.2384</v>
       </c>
       <c r="V14" t="n">
         <v>0.6597</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0046</v>
+        <v>0.4139</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5661</v>
+        <v>-0.2658</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5707</v>
+        <v>0.6798</v>
       </c>
       <c r="G15" t="n">
         <v>0.159</v>
@@ -1624,13 +1624,13 @@
         <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0485</v>
+        <v>0.3609</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1211</v>
+        <v>0.1792</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0727</v>
+        <v>0.1817</v>
       </c>
       <c r="V15" t="n">
         <v>0.2821</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9665</v>
+        <v>-1.2252</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9715</v>
+        <v>0.7755</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005</v>
+        <v>-2.0007</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.3547</v>
+        <v>-2.9456</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2065</v>
+        <v>2.2335</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.1482</v>
+        <v>-5.1791</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.5609</v>
+        <v>1.2602</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.0153</v>
+        <v>1.9403</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5455</v>
+        <v>-0.6801</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7939</v>
+        <v>-4.2058</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1912</v>
+        <v>0.2933</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.6027</v>
+        <v>-4.4991</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1344</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9105</v>
+        <v>-1.1642</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9105</v>
+        <v>3.2985</v>
       </c>
       <c r="S16" t="n">
-        <v>5.4838</v>
+        <v>-0.9304</v>
       </c>
       <c r="T16" t="n">
-        <v>5.5954</v>
+        <v>-0.1189</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1117</v>
+        <v>-0.8114</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0955</v>
+        <v>0.5164</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0955</v>
+        <v>0.7985</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7262</v>
+        <v>-3.2729</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4257</v>
+        <v>-1.0312</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3006</v>
+        <v>-2.2418</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.9456</v>
+        <v>-1.9542</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2335</v>
+        <v>-0.4638</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.1791</v>
+        <v>-1.4904</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2602</v>
+        <v>0.0206</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9403</v>
+        <v>0.0206</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6801</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.2058</v>
+        <v>-1.9748</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2933</v>
+        <v>-0.4844</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.4991</v>
+        <v>-1.4904</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2985</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.4313</v>
+        <v>-0.3485</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3201</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1112</v>
+        <v>-0.2669</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5164</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7985</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.373</v>
+        <v>-4.4629</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1313</v>
+        <v>-1.9558</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2418</v>
+        <v>-2.5071</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9542</v>
+        <v>-3.5138</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4638</v>
+        <v>0.7728</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4904</v>
+        <v>-4.2865</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0206</v>
+        <v>-0.1864</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0206</v>
+        <v>0.552</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.7385</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9748</v>
+        <v>-3.3273</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4844</v>
+        <v>0.2208</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4904</v>
+        <v>-3.5481</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9702</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-3.1045</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.7164</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4486</v>
+        <v>-0.5611</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1817</v>
+        <v>-0.1708</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2669</v>
+        <v>-0.3903</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.5451</v>
+        <v>-4.7881</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2561</v>
+        <v>-4.575</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2891</v>
+        <v>-0.2131</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5138</v>
+        <v>-6.3547</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7728</v>
+        <v>-3.2065</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.2865</v>
+        <v>-3.1482</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1864</v>
+        <v>-3.5609</v>
       </c>
       <c r="K19" t="n">
-        <v>0.552</v>
+        <v>-3.0153</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7385</v>
+        <v>-0.5455</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3273</v>
+        <v>-2.7939</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2208</v>
+        <v>-0.1912</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.5481</v>
+        <v>-2.6027</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1045</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7164</v>
+        <v>2.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6433</v>
+        <v>1.6622</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4711</v>
+        <v>1.9919</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1722</v>
+        <v>-0.3297</v>
       </c>
       <c r="V19" t="n">
+        <v>-0.0955</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.0955</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.506</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.506</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.8309</v>
+        <v>-6.830900000000002</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6503</v>
+        <v>1.650399999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.481400000000001</v>
+        <v>-8.481199999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-13.6096</v>
@@ -2005,7 +2005,7 @@
         <v>-20.4934</v>
       </c>
       <c r="P20" t="n">
-        <v>6.7911</v>
+        <v>6.791099999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>-12.6122</v>
@@ -2014,13 +2014,13 @@
         <v>19.4031</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7907</v>
+        <v>0.7906999999999998</v>
       </c>
       <c r="T20" t="n">
-        <v>2.803599999999999</v>
+        <v>2.8037</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.0129</v>
+        <v>-2.013</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8030000000000003</v>
